--- a/data/raw/sales/Week 30/White_Mulberry/Seller Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 30/White_Mulberry/Seller Sales (SP-API).xlsx
@@ -1,114 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
-  <si>
-    <t>SKU</t>
-  </si>
-  <si>
-    <t>(Child) ASIN</t>
-  </si>
-  <si>
-    <t>(Parent) ASIN</t>
-  </si>
-  <si>
-    <t>Brand</t>
-  </si>
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Units Ordered</t>
-  </si>
-  <si>
-    <t>Ordered Product Sales</t>
-  </si>
-  <si>
-    <t>Sessions</t>
-  </si>
-  <si>
-    <t>Page Views</t>
-  </si>
-  <si>
-    <t>Buy Box Percentage</t>
-  </si>
-  <si>
-    <t>Seller Account</t>
-  </si>
-  <si>
-    <t>Week</t>
-  </si>
-  <si>
-    <t>WindowStart</t>
-  </si>
-  <si>
-    <t>WindowEnd</t>
-  </si>
-  <si>
-    <t>FBA79478</t>
-  </si>
-  <si>
-    <t>B0DB5W4TCP</t>
-  </si>
-  <si>
-    <t>White Mulberry</t>
-  </si>
-  <si>
-    <t>WM-HA1M-BK</t>
-  </si>
-  <si>
-    <t>CAMBIUMRETAIL</t>
-  </si>
-  <si>
-    <t>2026-07-19</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -116,36 +42,85 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -433,99 +408,1827 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>(Child) ASIN</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>(Parent) ASIN</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Units Ordered</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Ordered Product Sales</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Sessions</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Page Views</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Buy Box Percentage</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Seller Account</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>WindowStart</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>WindowEnd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FBA79478</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>WM-HA1M-BK</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>259</v>
+      </c>
+      <c r="I2" t="n">
+        <v>336</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>CAMBIUMRETAIL</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>30</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FBA79476</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>WM-GS1M-BK</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G3" t="n">
+        <v>2414.41</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2495</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3452</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>30</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FBA79477</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>WM-GS2M-BK</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11183.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>831</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1158</v>
+      </c>
+      <c r="J4" t="n">
+        <v>43.92</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>30</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FBA79478</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>WM-HA1M-BK</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>259</v>
+      </c>
+      <c r="I5" t="n">
+        <v>336</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>30</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FBA79479</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>WM-HA2M-BK</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G6" t="n">
+        <v>1863.56</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1038</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1451</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>30</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FBA79613</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MS1ML</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>20</v>
+      </c>
+      <c r="G7" t="n">
+        <v>32187.29</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2987</v>
+      </c>
+      <c r="J7" t="n">
+        <v>45.15</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>30</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FBA79612</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>WM1ML</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G8" t="n">
+        <v>8387.290000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>379</v>
+      </c>
+      <c r="I8" t="n">
+        <v>496</v>
+      </c>
+      <c r="J8" t="n">
+        <v>99.31999999999999</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>30</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FBA79615</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>VLMS1ML</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11809.32</v>
+      </c>
+      <c r="H9" t="n">
+        <v>383</v>
+      </c>
+      <c r="I9" t="n">
+        <v>478</v>
+      </c>
+      <c r="J9" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>30</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FBA79616</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B0DP3194QN</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0DP3194QN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HD1ML</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>30</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FBA79617</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HDWF1ML</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>929</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1258</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>30</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FBA79790</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TVLF1ML</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3850</v>
+      </c>
+      <c r="H12" t="n">
+        <v>131</v>
+      </c>
+      <c r="I12" t="n">
+        <v>179</v>
+      </c>
+      <c r="J12" t="n">
+        <v>100</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>30</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FBK79788</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TVCT1ML</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2333.9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>165</v>
+      </c>
+      <c r="I13" t="n">
+        <v>222</v>
+      </c>
+      <c r="J13" t="n">
+        <v>99.06999999999999</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>30</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FBK79789</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TVMF1ML</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>34</v>
+      </c>
+      <c r="G14" t="n">
+        <v>18123.73</v>
+      </c>
+      <c r="H14" t="n">
+        <v>608</v>
+      </c>
+      <c r="I14" t="n">
+        <v>932</v>
+      </c>
+      <c r="J14" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>30</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FBK79784</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B0FN4FHH5Y</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0FN4FHH5Y</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>POS2M</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>38</v>
+      </c>
+      <c r="I15" t="n">
+        <v>45</v>
+      </c>
+      <c r="J15" t="n">
+        <v>100</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>30</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FBK79786</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B0FN4FPJ83</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0FN4FPJ83</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>POSS-01</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>11858.47</v>
+      </c>
+      <c r="H16" t="n">
+        <v>89</v>
+      </c>
+      <c r="I16" t="n">
+        <v>130</v>
+      </c>
+      <c r="J16" t="n">
+        <v>100</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>30</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FBK79787</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B0FN4GQ9HT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0FN4GQ9HT</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TVCF1ML</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3045.76</v>
+      </c>
+      <c r="H17" t="n">
+        <v>330</v>
+      </c>
+      <c r="I17" t="n">
+        <v>473</v>
+      </c>
+      <c r="J17" t="n">
+        <v>100</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>30</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FBK79791</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>B0FN4HDM6Z</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0FN4HDM6Z</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TVFM1ML</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>12</v>
+      </c>
+      <c r="G18" t="n">
+        <v>18294.92</v>
+      </c>
+      <c r="H18" t="n">
+        <v>369</v>
+      </c>
+      <c r="I18" t="n">
+        <v>576</v>
+      </c>
+      <c r="J18" t="n">
+        <v>100</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>30</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FBK79792</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>B0FN4JG97R</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0FN4JG97R</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>HDMSP1ML</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9520.34</v>
+      </c>
+      <c r="H19" t="n">
+        <v>260</v>
+      </c>
+      <c r="I19" t="n">
+        <v>293</v>
+      </c>
+      <c r="J19" t="n">
+        <v>99.64</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>30</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FBK79793</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>B0FN81FD8M</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0FN81FD8M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>HDGS1ML</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13832.2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>60</v>
+      </c>
+      <c r="I20" t="n">
+        <v>81</v>
+      </c>
+      <c r="J20" t="n">
+        <v>100</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>30</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FBA76417</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>WM-LOD-WH</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>35165.25</v>
+      </c>
+      <c r="H21" t="n">
+        <v>972</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1416</v>
+      </c>
+      <c r="J21" t="n">
+        <v>84.72</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>WHITEMULBERRY</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>30</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FBA76418</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>B0BFVNS8HS</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0BFVNS8HS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>WM-LOD-IN</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G22" t="n">
+        <v>28132.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>614</v>
+      </c>
+      <c r="I22" t="n">
+        <v>749</v>
+      </c>
+      <c r="J22" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>WHITEMULBERRY</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>30</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FBA76416</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>B0BFW59TRG</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0BFW59TRG</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>WM-LOD-BK</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2">
+      <c r="G23" t="n">
+        <v>28055.11</v>
+      </c>
+      <c r="H23" t="n">
+        <v>777</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1003</v>
+      </c>
+      <c r="J23" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>WHITEMULBERRY</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>30</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FBA76415</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>WM-LOD-CF</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>14062.71</v>
+      </c>
+      <c r="H24" t="n">
+        <v>948</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1320</v>
+      </c>
+      <c r="J24" t="n">
+        <v>52.63</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>WHITEMULBERRY</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>30</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FBA79167</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>WM-GD07-CB</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>32</v>
+      </c>
+      <c r="G25" t="n">
+        <v>225905.93</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4984</v>
+      </c>
+      <c r="I25" t="n">
+        <v>7047</v>
+      </c>
+      <c r="J25" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>WHITEMULBERRY</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>30</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FBA79178</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>B0CPT2NY5M</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0CPT2NY5M</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>WM-SE08-WH</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>24252.54</v>
+      </c>
+      <c r="H26" t="n">
+        <v>50</v>
+      </c>
+      <c r="I26" t="n">
+        <v>84</v>
+      </c>
+      <c r="J26" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>WHITEMULBERRY</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>30</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FBA79175</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>B0CPT2YJX2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B0CPT2YJX2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>WM-SMD09-WH</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>0</v>
       </c>
-      <c r="G2">
+      <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H2">
-        <v>259</v>
-      </c>
-      <c r="I2">
-        <v>336</v>
-      </c>
-      <c r="J2">
+      <c r="H27" t="n">
+        <v>88</v>
+      </c>
+      <c r="I27" t="n">
+        <v>103</v>
+      </c>
+      <c r="J27" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>WHITEMULBERRY</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>30</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>FBA79179</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>B0CPT3Q25C</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B0CPT3Q25C</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>WM-SE08-CF</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="n">
+        <v>50850.85</v>
+      </c>
+      <c r="H28" t="n">
+        <v>312</v>
+      </c>
+      <c r="I28" t="n">
+        <v>469</v>
+      </c>
+      <c r="J28" t="n">
+        <v>84.14</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>WHITEMULBERRY</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>30</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FBA79617</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>HDWF1ML</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2">
-        <v>30</v>
-      </c>
-      <c r="M2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" t="s">
-        <v>20</v>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>929</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1258</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>WHITEMULBERRY</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>30</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FBA79661</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>B0DQ51R95T</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0DQ51R95T</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>WM-MODL-BK</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10168.64</v>
+      </c>
+      <c r="H30" t="n">
+        <v>365</v>
+      </c>
+      <c r="I30" t="n">
+        <v>564</v>
+      </c>
+      <c r="J30" t="n">
+        <v>100</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>WHITEMULBERRY</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>30</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>